--- a/job application performance tracker.xlsx
+++ b/job application performance tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>Application_Id</t>
   </si>
@@ -46,6 +46,9 @@
     <t>City</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN-B NET ZERO</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>Baienfurt</t>
   </si>
   <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
     <t>Persis</t>
   </si>
   <si>
@@ -91,10 +97,28 @@
     <t>https://www.linkedin.com/jobs/view/4433086640/</t>
   </si>
   <si>
-    <t>Germna</t>
-  </si>
-  <si>
     <t>Mannheim</t>
+  </si>
+  <si>
+    <t>Amadeus Fire</t>
+  </si>
+  <si>
+    <t>BI Analyst (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4430980511</t>
+  </si>
+  <si>
+    <t>CGI</t>
+  </si>
+  <si>
+    <t>Senior Power BI Entwickler / Consultant</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4383819658/</t>
+  </si>
+  <si>
+    <t>Leipzig</t>
   </si>
 </sst>
 </file>
@@ -104,7 +128,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -112,11 +136,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color rgb="FF222222"/>
       <name val="Arial"/>
     </font>
@@ -132,6 +162,16 @@
       <b/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="-apple-system"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -154,27 +194,36 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -395,6 +444,7 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="14.88"/>
     <col customWidth="1" min="3" max="4" width="18.88"/>
+    <col customWidth="1" min="5" max="5" width="31.25"/>
     <col customWidth="1" min="8" max="8" width="38.5"/>
     <col customWidth="1" min="9" max="9" width="36.75"/>
   </cols>
@@ -433,164 +483,248 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>46194.0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="I2" s="4" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="G2" s="2"/>
+      <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>1.0</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>46196.0</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="K3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46199.0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46199.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46199.0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="K5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46200.0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="J6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46199.0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="L6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B7" s="3">
         <v>46200.0</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46200.0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="J7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="I2"/>
     <hyperlink r:id="rId2" ref="I5"/>
     <hyperlink r:id="rId3" ref="I7"/>
+    <hyperlink r:id="rId4" ref="I8"/>
+    <hyperlink r:id="rId5" ref="I9"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/job application performance tracker.xlsx
+++ b/job application performance tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
   <si>
     <t>Application_Id</t>
   </si>
@@ -119,6 +119,72 @@
   </si>
   <si>
     <t>Leipzig</t>
+  </si>
+  <si>
+    <t>Intersport EG</t>
+  </si>
+  <si>
+    <t>Data Analyst -Business Intellegence</t>
+  </si>
+  <si>
+    <t>Heilbronn</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>KVRLP</t>
+  </si>
+  <si>
+    <t>BI-Entwickler</t>
+  </si>
+  <si>
+    <t>Mainz</t>
+  </si>
+  <si>
+    <t>TSO Data</t>
+  </si>
+  <si>
+    <t>Software Entwickler</t>
+  </si>
+  <si>
+    <t>Osnabruck</t>
+  </si>
+  <si>
+    <t>Bosch</t>
+  </si>
+  <si>
+    <t>Data Analyst (w/m/div.) - Commerical Excellence</t>
+  </si>
+  <si>
+    <t>https://jobs.smartrecruiters.com/BoschGroup/744000134731359-data-analyst-w-m-div-commerical-excellence?utm_source=linkedin&amp;utm_medium=jobslot&amp;trid=2d92f286-613b-4daf-9dfa-6340ffbecf73</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>Business Analyst Schwerpunkt Europäische Business Units</t>
+  </si>
+  <si>
+    <t>https://jobs.smartrecruiters.com/BoschGroup/744000133951889-business-analyst-w-m-div-schwerpunkt-europaische-business-units?utm_source=linkedin&amp;utm_medium=jobslot&amp;trid=2d92f286-613b-4daf-9dfa-6340ffbecf73</t>
+  </si>
+  <si>
+    <t>BESTSECRET</t>
+  </si>
+  <si>
+    <t>Data Analyst Loss Prevention</t>
+  </si>
+  <si>
+    <t>https://careersportal.bestsecret.com/job/Data-Analyst-Loss-Prevention-%28All-Genders%29/943-en_US</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>DHL</t>
+  </si>
+  <si>
+    <t>Business Analyst</t>
   </si>
 </sst>
 </file>
@@ -444,7 +510,7 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="14.88"/>
     <col customWidth="1" min="3" max="4" width="18.88"/>
-    <col customWidth="1" min="5" max="5" width="31.25"/>
+    <col customWidth="1" min="5" max="5" width="48.88"/>
     <col customWidth="1" min="8" max="8" width="38.5"/>
     <col customWidth="1" min="9" max="9" width="36.75"/>
   </cols>
@@ -714,8 +780,388 @@
         <v>13</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46198.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46196.0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="18">
-      <c r="B18" s="2"/>
+      <c r="A18" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46197.0</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46203.0</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46203.0</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -724,7 +1170,13 @@
     <hyperlink r:id="rId3" ref="I7"/>
     <hyperlink r:id="rId4" ref="I8"/>
     <hyperlink r:id="rId5" ref="I9"/>
+    <hyperlink r:id="rId6" ref="I14"/>
+    <hyperlink r:id="rId7" ref="I15"/>
+    <hyperlink r:id="rId8" ref="I18"/>
+    <hyperlink r:id="rId9" ref="I19"/>
+    <hyperlink r:id="rId10" ref="I20"/>
+    <hyperlink r:id="rId11" ref="I23"/>
   </hyperlinks>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/job application performance tracker.xlsx
+++ b/job application performance tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="83">
   <si>
     <t>Application_Id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Category</t>
   </si>
   <si>
+    <t>Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN-B NET ZERO</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>Berlin</t>
   </si>
   <si>
+    <t>Linked In</t>
+  </si>
+  <si>
     <t>HR Contacted</t>
   </si>
   <si>
@@ -88,6 +94,9 @@
     <t>Persis</t>
   </si>
   <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
     <t>Randstad</t>
   </si>
   <si>
@@ -185,6 +194,72 @@
   </si>
   <si>
     <t>Business Analyst</t>
+  </si>
+  <si>
+    <t>Francotyp-Postalia Holding AG</t>
+  </si>
+  <si>
+    <t>https://azolver.bamboohr.com/careers/202</t>
+  </si>
+  <si>
+    <t>Stepstone</t>
+  </si>
+  <si>
+    <t>INP Deutschland</t>
+  </si>
+  <si>
+    <t>Data Analyst Energieprojekte (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4432350446/</t>
+  </si>
+  <si>
+    <t>Nexia GMBH</t>
+  </si>
+  <si>
+    <t>Finance Data Analyst</t>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Data-Analyst-m-w-d-mit-Schwerpunkt-MS-Power-BI-Frankfurt-am-Main-Nexia-GmbH-Wirtschaftspruefungsgesellschaft-Steuerberatungsgesellschaft--14221237-inline.html</t>
+  </si>
+  <si>
+    <t>Frankfurt</t>
+  </si>
+  <si>
+    <t>Blue Orange</t>
+  </si>
+  <si>
+    <t>Power BI Specialist</t>
+  </si>
+  <si>
+    <t>DIS AG</t>
+  </si>
+  <si>
+    <t>Data Engineer (Microsoft Stack)</t>
+  </si>
+  <si>
+    <t>https://jobs.dis-ag.com/job/7babc774-0cce-4272-b3d1-7abfddfcf8e4/data-scientist-berlin-43104?amp%3Bcdx_source=website_organic&amp;cdx_source=website_organic&amp;_gl=1*t5ldy8*_gcl_au*NDk5NzU4MTU0LjE3ODI5Mzg3MzU.</t>
+  </si>
+  <si>
+    <t>Horvath</t>
+  </si>
+  <si>
+    <t>Consultant (w/m/d) BI &amp; Analytics (all levels)</t>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Consultant-w-m-d-BI-Analytics-all-levels-Stuttgart-Berlin-Duesseldorf-Frankfurt-Hamburg-Muenchen-Horv%C3%A1th--14171418-inline.html</t>
+  </si>
+  <si>
+    <t>4G Group</t>
+  </si>
+  <si>
+    <t>Senior Consultant BI</t>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Senior-Consultant-BI-Business-Intelligence-w-d-m-Muenchen-Berlin-4C-GROUP-AG--13405438-inline.html?rltr=8_8_25_seorl_a_0_0_5_0_0_0</t>
+  </si>
+  <si>
+    <t>BI Analyst</t>
   </si>
 </sst>
 </file>
@@ -552,6 +627,9 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -561,27 +639,30 @@
         <v>46194.0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2"/>
       <c r="I2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -592,21 +673,24 @@
         <v>46196.0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -617,23 +701,26 @@
         <v>46199.0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2">
         <v>1.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -644,27 +731,30 @@
         <v>46199.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2"/>
       <c r="I5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -675,21 +765,27 @@
         <v>46200.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -700,26 +796,29 @@
         <v>46200.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -730,25 +829,28 @@
         <v>46201.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -759,25 +861,28 @@
         <v>46202.0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +893,25 @@
         <v>46198.0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -814,22 +922,25 @@
         <v>46202.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -840,22 +951,25 @@
         <v>46195.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -866,22 +980,25 @@
         <v>46202.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -892,25 +1009,28 @@
         <v>46202.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -921,26 +1041,29 @@
         <v>46202.0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -951,22 +1074,25 @@
         <v>46196.0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -977,22 +1103,25 @@
         <v>46202.0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1003,25 +1132,28 @@
         <v>46202.0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1032,25 +1164,28 @@
         <v>46202.0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1061,25 +1196,28 @@
         <v>46202.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1090,22 +1228,25 @@
         <v>46197.0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1116,22 +1257,25 @@
         <v>46203.0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1142,25 +1286,278 @@
         <v>46203.0</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46203.0</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1573,13 @@
     <hyperlink r:id="rId9" ref="I19"/>
     <hyperlink r:id="rId10" ref="I20"/>
     <hyperlink r:id="rId11" ref="I23"/>
+    <hyperlink r:id="rId12" ref="I24"/>
+    <hyperlink r:id="rId13" ref="I25"/>
+    <hyperlink r:id="rId14" ref="I26"/>
+    <hyperlink r:id="rId15" ref="I29"/>
+    <hyperlink r:id="rId16" ref="I30"/>
+    <hyperlink r:id="rId17" ref="I31"/>
   </hyperlinks>
-  <drawing r:id="rId12"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
--- a/job application performance tracker.xlsx
+++ b/job application performance tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="90">
   <si>
     <t>Application_Id</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Platform</t>
   </si>
   <si>
+    <t>Linked In Message</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN-B NET ZERO</t>
   </si>
   <si>
@@ -241,6 +244,9 @@
     <t>https://jobs.dis-ag.com/job/7babc774-0cce-4272-b3d1-7abfddfcf8e4/data-scientist-berlin-43104?amp%3Bcdx_source=website_organic&amp;cdx_source=website_organic&amp;_gl=1*t5ldy8*_gcl_au*NDk5NzU4MTU0LjE3ODI5Mzg3MzU.</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Horvath</t>
   </si>
   <si>
@@ -260,6 +266,21 @@
   </si>
   <si>
     <t>BI Analyst</t>
+  </si>
+  <si>
+    <t>ADAC Niedersachsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior BI Controller (m/w/d) </t>
+  </si>
+  <si>
+    <t>Rethen</t>
+  </si>
+  <si>
+    <t>Schleich</t>
+  </si>
+  <si>
+    <t>BI &amp; Analytics Engineer</t>
   </si>
 </sst>
 </file>
@@ -269,7 +290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -314,6 +335,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF222222"/>
+      <name val="AvenirLTStd-Light"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -335,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -364,6 +393,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -588,6 +623,7 @@
     <col customWidth="1" min="5" max="5" width="48.88"/>
     <col customWidth="1" min="8" max="8" width="38.5"/>
     <col customWidth="1" min="9" max="9" width="36.75"/>
+    <col customWidth="1" min="14" max="14" width="20.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -630,6 +666,9 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -639,30 +678,30 @@
         <v>46194.0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2"/>
       <c r="I2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -673,24 +712,24 @@
         <v>46196.0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -701,26 +740,26 @@
         <v>46199.0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="2">
         <v>1.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -731,30 +770,30 @@
         <v>46199.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2"/>
       <c r="I5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -765,27 +804,27 @@
         <v>46200.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -796,29 +835,29 @@
         <v>46200.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -829,28 +868,28 @@
         <v>46201.0</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -861,28 +900,28 @@
         <v>46202.0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -893,25 +932,25 @@
         <v>46198.0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -922,25 +961,25 @@
         <v>46202.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -951,25 +990,25 @@
         <v>46195.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -980,25 +1019,25 @@
         <v>46202.0</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1009,28 +1048,28 @@
         <v>46202.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1041,29 +1080,29 @@
         <v>46202.0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1074,25 +1113,25 @@
         <v>46196.0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1103,25 +1142,25 @@
         <v>46202.0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1132,28 +1171,28 @@
         <v>46202.0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1164,28 +1203,28 @@
         <v>46202.0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="L19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1196,28 +1235,28 @@
         <v>46202.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1228,25 +1267,25 @@
         <v>46197.0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1257,25 +1296,25 @@
         <v>46203.0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1286,28 +1325,28 @@
         <v>46203.0</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="L23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1318,28 +1357,28 @@
         <v>46203.0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -1350,28 +1389,28 @@
         <v>46204.0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1382,28 +1421,28 @@
         <v>46204.0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -1414,25 +1453,25 @@
         <v>46195.0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1443,25 +1482,25 @@
         <v>46204.0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1472,28 +1511,31 @@
         <v>46204.0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="30">
@@ -1504,28 +1546,28 @@
         <v>46204.0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
@@ -1536,28 +1578,276 @@
         <v>46204.0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46198.0</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46195.0</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1869,11 @@
     <hyperlink r:id="rId15" ref="I29"/>
     <hyperlink r:id="rId16" ref="I30"/>
     <hyperlink r:id="rId17" ref="I31"/>
+    <hyperlink r:id="rId18" ref="I34"/>
+    <hyperlink r:id="rId19" ref="I35"/>
+    <hyperlink r:id="rId20" ref="I36"/>
+    <hyperlink r:id="rId21" ref="I39"/>
   </hyperlinks>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
--- a/job application performance tracker.xlsx
+++ b/job application performance tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="166">
   <si>
     <t>Application_Id</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Linked In Message</t>
   </si>
   <si>
+    <t>AI Tool</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN-B NET ZERO</t>
   </si>
   <si>
@@ -281,6 +284,303 @@
   </si>
   <si>
     <t>BI &amp; Analytics Engineer</t>
+  </si>
+  <si>
+    <t>Helm</t>
+  </si>
+  <si>
+    <t>(Junior) Business Intelligence Developer - Data Warehouse (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://jobs.helmag.com/job/Hamburg-%28Junior%29-Business-Intelligence-Developer-Data-Warehouse-%28mwd%29-20097/1349353255/</t>
+  </si>
+  <si>
+    <t>CGM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>Data Engineer BI (m/w/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://cgm.wd3.myworkdayjobs.com/de-DE/cgm/job/Waldems/Data-Engineer-BI--m-w-d-_JR109347?source=LinkedIn</t>
+  </si>
+  <si>
+    <t>Waldems</t>
+  </si>
+  <si>
+    <t>Team SE</t>
+  </si>
+  <si>
+    <t>Junior BI Specialist (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://karriere.team.de/serviceeinheit/offer/junior-bi-specialist-m-w-d/9a3a3ca5-0ae6-44e0-955f-5aafcc37cc3b</t>
+  </si>
+  <si>
+    <t>Flensburg</t>
+  </si>
+  <si>
+    <t>Indeed</t>
+  </si>
+  <si>
+    <t>HSE Home Shopping Europe GmbH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Expert BI &amp; Analytics (m/f/d) </t>
+  </si>
+  <si>
+    <t>https://jobs.hse.com/stellenangebote/digital/junior-expert-bi-und-analytics-mfd-3619?lang=en&amp;_gl=1*wopf8u*_up*MQ..*_ga*MjgzNDI4NzE0LjE3Nzk0Mjg4MTQ.*_ga_E66CVEM40J*czE3Nzk0Mjg4MTMkbzEkZzEkdDE3Nzk0Mjg4MjUkajQ4JGwwJGgw</t>
+  </si>
+  <si>
+    <t>Ismaning</t>
+  </si>
+  <si>
+    <t>SPIE</t>
+  </si>
+  <si>
+    <t>Data Analyst - Power BI &amp; IOT m/w/d</t>
+  </si>
+  <si>
+    <t>https://spie.de/karriere/stellenangebote/Data-Analyst---Power-BI---IOT-m-w-d-2026-0557</t>
+  </si>
+  <si>
+    <t>Köln</t>
+  </si>
+  <si>
+    <t>Schluckwerder GmbH</t>
+  </si>
+  <si>
+    <t>Controller / BI Analyst</t>
+  </si>
+  <si>
+    <t>https://www.efinancialcareers.de/jobs-Germany-Adendorf-Junior_Controller_-_Sales_Controlling__BI_Tooling_mwd.id24480990?utm_campaign=JS_DE_ALLJOBS&amp;utm_medium=PD_AG_XING&amp;utm_source=EMEA_DE_GER&amp;utm_term=xing-germany-cpc_eur</t>
+  </si>
+  <si>
+    <t>Adendorf</t>
+  </si>
+  <si>
+    <t>Xing</t>
+  </si>
+  <si>
+    <t>Hilscher Gesellschaft für Systemautomation mbH</t>
+  </si>
+  <si>
+    <t>Data Analyst / Power BI Professional (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://www.hilscher.com/de/karriere/data-analyst-/-power-bi-professional-m/w/d</t>
+  </si>
+  <si>
+    <t>Hattersheim am Main</t>
+  </si>
+  <si>
+    <t>Siemens Healthineers</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>Supply Chain Specialist – Order Management &amp; Produktionssteuerung (w/m/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://jobs.siemens-healthineers.com/en_US/searchjobs/JobDetailApplied?folderId=512742</t>
+  </si>
+  <si>
+    <t>Forcheim</t>
+  </si>
+  <si>
+    <t>axicorp GmbH-Teams</t>
+  </si>
+  <si>
+    <t>Microsoft BI Entwickler (m/w/d)</t>
+  </si>
+  <si>
+    <t>https://jobs.dermapharm.com/de/job-detail/microsoft-bi-entwickler-mwd/</t>
+  </si>
+  <si>
+    <t>Friedrichsdorf</t>
+  </si>
+  <si>
+    <t>Ib vogt</t>
+  </si>
+  <si>
+    <t>Business Analyst, Data &amp; AI (m/f/d)</t>
+  </si>
+  <si>
+    <t>https://www.ibvogt.com/vacancy/business-analyst-data-ai-m-f-d/</t>
+  </si>
+  <si>
+    <t>The Quality Group GmbH</t>
+  </si>
+  <si>
+    <t>(Junior) Insights &amp; Analytics Consultant</t>
+  </si>
+  <si>
+    <t>WWF</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="&quot;Relative Pro&quot;, Arial, sans-serif"/>
+        <color rgb="FF000000"/>
+        <sz val="5.0"/>
+        <u/>
+      </rPr>
+      <t>Enterprise Data &amp; Systems Specialist (Microsoft) (m/w/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Enterprise-Data-Systems-Specialist-Microsoft-m-w-d-Berlin-WWF-Deutschland--14128329-inline.html</t>
+  </si>
+  <si>
+    <t>Westpress</t>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Data-Analyst-m-w-d-Hamm-Westpress-GmbH-Co-KG--14233397-inline.html</t>
+  </si>
+  <si>
+    <t>Hamm</t>
+  </si>
+  <si>
+    <t>Dr. Sasse Gruppe</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>Digital Automation &amp; AI Professional (m/w/d) – Automation, Workflow &amp; Power Platform</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.stepstone.de/stellenangebote--Digital-Automation-AI-Professional-m-w-d-Automation-Workflow-Power-Platform-Muenchen-Berlin-Dr-Sasse-Gruppe--14190744-inline.html?rltr=17_17_25_seorl_a_0_0_0_0_1_0</t>
+  </si>
+  <si>
+    <t>ML/AI</t>
+  </si>
+  <si>
+    <t>Thinkcel</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4419344019</t>
+  </si>
+  <si>
+    <t>Ml/AI</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>Arineo GmbH</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Consultant Data Analytics Microsoft Power BI / Fabric</t>
+  </si>
+  <si>
+    <t>https://www.heyjobs.co/en-de/jobs/79268fe2-2f53-45aa-b07a-b2403b6f95fe?ri=1b83997f-0c15-4ee6-bb42-c5425015910c</t>
+  </si>
+  <si>
+    <t>Heyjobs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Ubuntu, Oxygen, Cantarell, &quot;Fira Sans&quot;, &quot;Droid Sans&quot;, &quot;Helvetica Neue&quot;, Arial, sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>nexnet</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>BI Engineer / Data Warehouse Developer (m/w/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4434541199/</t>
+  </si>
+  <si>
+    <t>codex</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Business Intelligence Analyst</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4440026683/</t>
+  </si>
+  <si>
+    <t>adesso</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="system-ui, -apple-system, BlinkMacSystemFont, &quot;Segoe UI&quot;, Roboto, Ubuntu, Oxygen, Cantarell, &quot;Fira Sans&quot;, &quot;Droid Sans&quot;, &quot;Helvetica Neue&quot;, Arial, sans-serif, &quot;Apple Color Emoji&quot;, &quot;Segoe UI Emoji&quot;, &quot;Segoe UI Symbol&quot;"/>
+        <color rgb="FF1155CC"/>
+        <sz val="12.0"/>
+        <u/>
+      </rPr>
+      <t>Senior Consultant Microsoft Fabric (all genders)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4439404949/</t>
+  </si>
+  <si>
+    <t>Karlsruhe</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>Supply Chain Specialist – Order Management &amp; Produktionssteuerung (w/m/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sonova</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Senior Data Analyst (m/f/d)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4440524874/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4430485919/</t>
+  </si>
+  <si>
+    <t>Claude</t>
   </si>
 </sst>
 </file>
@@ -290,7 +590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="32">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -343,8 +643,115 @@
       <color rgb="FF222222"/>
       <name val="AvenirLTStd-Light"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF333333"/>
+      <name val="Lato"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF252525"/>
+      <name val="Lato"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Barlow"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF0F1E5A"/>
+      <name val="Barlow"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF292929"/>
+      <name val="&quot;Source Sans 3&quot;"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF4E6677"/>
+      <name val="BasierSquare"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF101820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF101820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1A1A18"/>
+      <name val="Lato"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
+      <name val="Lato"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FF1A1A18"/>
+      <name val="Lato"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF1F2A4E"/>
+      <name val="&quot;Open Sans&quot;"/>
+    </font>
+    <font>
+      <sz val="7.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="5.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Relative Pro&quot;"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Relative Pro&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,6 +764,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAECEC"/>
+        <bgColor rgb="FFEAECEC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -364,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -399,6 +818,69 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -669,6 +1151,9 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -678,30 +1163,30 @@
         <v>46194.0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2"/>
       <c r="I2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -712,24 +1197,24 @@
         <v>46196.0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -740,26 +1225,26 @@
         <v>46199.0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2">
         <v>1.0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -770,30 +1255,30 @@
         <v>46199.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2"/>
       <c r="I5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -804,27 +1289,27 @@
         <v>46200.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -835,29 +1320,29 @@
         <v>46200.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -868,28 +1353,28 @@
         <v>46201.0</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -900,28 +1385,28 @@
         <v>46202.0</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -932,25 +1417,25 @@
         <v>46198.0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -961,25 +1446,25 @@
         <v>46202.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -990,25 +1475,25 @@
         <v>46195.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1019,25 +1504,25 @@
         <v>46202.0</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1533,28 @@
         <v>46202.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1080,29 +1565,29 @@
         <v>46202.0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1113,25 +1598,25 @@
         <v>46196.0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1142,25 +1627,25 @@
         <v>46202.0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1171,28 +1656,28 @@
         <v>46202.0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1203,28 +1688,28 @@
         <v>46202.0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="L19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1235,28 +1720,28 @@
         <v>46202.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1267,25 +1752,25 @@
         <v>46197.0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1296,25 +1781,25 @@
         <v>46203.0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1325,28 +1810,28 @@
         <v>46203.0</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="L23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1357,28 +1842,28 @@
         <v>46203.0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -1389,28 +1874,28 @@
         <v>46204.0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1421,28 +1906,28 @@
         <v>46204.0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
@@ -1453,25 +1938,25 @@
         <v>46195.0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1482,25 +1967,25 @@
         <v>46204.0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -1511,31 +1996,31 @@
         <v>46204.0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -1546,28 +2031,28 @@
         <v>46204.0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
@@ -1578,28 +2063,28 @@
         <v>46204.0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
@@ -1610,25 +2095,25 @@
         <v>46198.0</v>
       </c>
       <c r="C32" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="M32" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -1639,25 +2124,25 @@
         <v>46206.0</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="M33" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34">
@@ -1668,28 +2153,28 @@
         <v>46204.0</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -1700,31 +2185,31 @@
         <v>46209.0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G35" s="2">
         <v>1.0</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -1735,28 +2220,28 @@
         <v>46206.0</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -1767,25 +2252,25 @@
         <v>46195.0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
@@ -1796,25 +2281,25 @@
         <v>46206.0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
@@ -1825,29 +2310,1107 @@
         <v>46202.0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M39" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B48" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="I48" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="B49" s="3">
+        <v>46210.0</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46210.0</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B52" s="3">
+        <v>46210.0</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46211.0</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46205.0</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46213.0</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B59" s="3">
+        <v>46214.0</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46215.0</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46215.0</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46215.0</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46216.0</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46216.0</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46210.0</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46217.0</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46204.0</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46209.0</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46202.0</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46213.0</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46219.0</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +3436,50 @@
     <hyperlink r:id="rId19" ref="I35"/>
     <hyperlink r:id="rId20" ref="I36"/>
     <hyperlink r:id="rId21" ref="I39"/>
+    <hyperlink r:id="rId22" ref="I40"/>
+    <hyperlink r:id="rId23" ref="E41"/>
+    <hyperlink r:id="rId24" ref="I41"/>
+    <hyperlink r:id="rId25" ref="I42"/>
+    <hyperlink r:id="rId26" ref="I43"/>
+    <hyperlink r:id="rId27" ref="I44"/>
+    <hyperlink r:id="rId28" ref="I45"/>
+    <hyperlink r:id="rId29" ref="I46"/>
+    <hyperlink r:id="rId30" ref="I47"/>
+    <hyperlink r:id="rId31" ref="I48"/>
+    <hyperlink r:id="rId32" ref="I49"/>
+    <hyperlink r:id="rId33" ref="I50"/>
+    <hyperlink r:id="rId34" ref="E51"/>
+    <hyperlink r:id="rId35" ref="I51"/>
+    <hyperlink r:id="rId36" ref="I52"/>
+    <hyperlink r:id="rId37" ref="I53"/>
+    <hyperlink r:id="rId38" ref="I54"/>
+    <hyperlink r:id="rId39" ref="E57"/>
+    <hyperlink r:id="rId40" ref="I57"/>
+    <hyperlink r:id="rId41" ref="I58"/>
+    <hyperlink r:id="rId42" ref="E59"/>
+    <hyperlink r:id="rId43" ref="I59"/>
+    <hyperlink r:id="rId44" ref="I60"/>
+    <hyperlink r:id="rId45" ref="C61"/>
+    <hyperlink r:id="rId46" ref="I61"/>
+    <hyperlink r:id="rId47" ref="C62"/>
+    <hyperlink r:id="rId48" ref="E62"/>
+    <hyperlink r:id="rId49" ref="I62"/>
+    <hyperlink r:id="rId50" ref="E63"/>
+    <hyperlink r:id="rId51" ref="I63"/>
+    <hyperlink r:id="rId52" ref="E64"/>
+    <hyperlink r:id="rId53" ref="I64"/>
+    <hyperlink r:id="rId54" ref="I65"/>
+    <hyperlink r:id="rId55" ref="E66"/>
+    <hyperlink r:id="rId56" ref="I66"/>
+    <hyperlink r:id="rId57" ref="E67"/>
+    <hyperlink r:id="rId58" ref="I67"/>
+    <hyperlink r:id="rId59" ref="I68"/>
+    <hyperlink r:id="rId60" ref="I69"/>
+    <hyperlink r:id="rId61" ref="I70"/>
+    <hyperlink r:id="rId62" ref="I71"/>
+    <hyperlink r:id="rId63" ref="I72"/>
+    <hyperlink r:id="rId64" ref="I73"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId65"/>
 </worksheet>
 </file>